--- a/rekap_wisuda_final.xlsx
+++ b/rekap_wisuda_final.xlsx
@@ -459,17 +459,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Predikat Wisuda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Tahun Wisuda</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Grade</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Predikat Wisuda</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,18 @@
       <c r="E2" t="n">
         <v>7</v>
       </c>
-      <c r="F2" t="n">
-        <v>2025</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="3">
@@ -527,18 +527,18 @@
       <c r="E3" t="n">
         <v>7</v>
       </c>
-      <c r="F3" t="n">
-        <v>2025</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="4">
@@ -561,18 +561,18 @@
       <c r="E4" t="n">
         <v>6</v>
       </c>
-      <c r="F4" t="n">
-        <v>2025</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="5">
@@ -595,18 +595,18 @@
       <c r="E5" t="n">
         <v>8</v>
       </c>
-      <c r="F5" t="n">
-        <v>2025</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H5" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="6">
@@ -629,18 +629,18 @@
       <c r="E6" t="n">
         <v>6</v>
       </c>
-      <c r="F6" t="n">
-        <v>2025</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H6" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="7">
@@ -663,18 +663,18 @@
       <c r="E7" t="n">
         <v>6</v>
       </c>
-      <c r="F7" t="n">
-        <v>2025</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H7" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="8">
@@ -697,18 +697,18 @@
       <c r="E8" t="n">
         <v>8</v>
       </c>
-      <c r="F8" t="n">
-        <v>2025</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H8" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="9">
@@ -731,18 +731,18 @@
       <c r="E9" t="n">
         <v>8</v>
       </c>
-      <c r="F9" t="n">
-        <v>2025</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="10">
@@ -765,18 +765,18 @@
       <c r="E10" t="n">
         <v>8</v>
       </c>
-      <c r="F10" t="n">
-        <v>2025</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H10" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="11">
@@ -799,18 +799,18 @@
       <c r="E11" t="n">
         <v>6</v>
       </c>
-      <c r="F11" t="n">
-        <v>2025</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="12">
@@ -833,18 +833,18 @@
       <c r="E12" t="n">
         <v>7</v>
       </c>
-      <c r="F12" t="n">
-        <v>2025</v>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="13">
@@ -867,18 +867,18 @@
       <c r="E13" t="n">
         <v>6</v>
       </c>
-      <c r="F13" t="n">
-        <v>2025</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H13" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="14">
@@ -901,18 +901,18 @@
       <c r="E14" t="n">
         <v>7</v>
       </c>
-      <c r="F14" t="n">
-        <v>2025</v>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
           <t>Cumlaude (Dengan Pujian)</t>
         </is>
+      </c>
+      <c r="H14" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="15">
@@ -935,18 +935,18 @@
       <c r="E15" t="n">
         <v>6</v>
       </c>
-      <c r="F15" t="n">
-        <v>2025</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="16">
@@ -955,7 +955,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>VINA ANJANI</t>
+          <t>Vina Anjani</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -969,18 +969,18 @@
       <c r="E16" t="n">
         <v>6</v>
       </c>
-      <c r="F16" t="n">
-        <v>2025</v>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H16" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="17">
@@ -1003,18 +1003,18 @@
       <c r="E17" t="n">
         <v>6</v>
       </c>
-      <c r="F17" t="n">
-        <v>2025</v>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="18">
@@ -1037,18 +1037,18 @@
       <c r="E18" t="n">
         <v>8</v>
       </c>
-      <c r="F18" t="n">
-        <v>2025</v>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
           <t>Cumlaude (Dengan Pujian)</t>
         </is>
+      </c>
+      <c r="H18" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="19">
@@ -1071,18 +1071,18 @@
       <c r="E19" t="n">
         <v>7</v>
       </c>
-      <c r="F19" t="n">
-        <v>2025</v>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H19" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="20">
@@ -1105,18 +1105,18 @@
       <c r="E20" t="n">
         <v>7</v>
       </c>
-      <c r="F20" t="n">
-        <v>2025</v>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
           <t>Cumlaude (Dengan Pujian)</t>
         </is>
+      </c>
+      <c r="H20" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="21">
@@ -1139,18 +1139,18 @@
       <c r="E21" t="n">
         <v>6</v>
       </c>
-      <c r="F21" t="n">
-        <v>2025</v>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H21" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="22">
@@ -1173,18 +1173,18 @@
       <c r="E22" t="n">
         <v>7</v>
       </c>
-      <c r="F22" t="n">
-        <v>2025</v>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="23">
@@ -1207,18 +1207,18 @@
       <c r="E23" t="n">
         <v>7</v>
       </c>
-      <c r="F23" t="n">
-        <v>2025</v>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="24">
@@ -1241,18 +1241,18 @@
       <c r="E24" t="n">
         <v>7</v>
       </c>
-      <c r="F24" t="n">
-        <v>2025</v>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
           <t>Cumlaude (Dengan Pujian)</t>
         </is>
+      </c>
+      <c r="H24" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="25">
@@ -1275,18 +1275,18 @@
       <c r="E25" t="n">
         <v>6</v>
       </c>
-      <c r="F25" t="n">
-        <v>2025</v>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H25" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="26">
@@ -1309,18 +1309,18 @@
       <c r="E26" t="n">
         <v>7</v>
       </c>
-      <c r="F26" t="n">
-        <v>2025</v>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H26" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="27">
@@ -1343,18 +1343,18 @@
       <c r="E27" t="n">
         <v>7</v>
       </c>
-      <c r="F27" t="n">
-        <v>2025</v>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H27" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="28">
@@ -1377,18 +1377,18 @@
       <c r="E28" t="n">
         <v>6</v>
       </c>
-      <c r="F28" t="n">
-        <v>2025</v>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H28" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="29">
@@ -1411,18 +1411,18 @@
       <c r="E29" t="n">
         <v>7</v>
       </c>
-      <c r="F29" t="n">
-        <v>2025</v>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="30">
@@ -1445,18 +1445,18 @@
       <c r="E30" t="n">
         <v>8</v>
       </c>
-      <c r="F30" t="n">
-        <v>2025</v>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H30" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="31">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>rafi</t>
+          <t>Rafi</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1479,18 +1479,18 @@
       <c r="E31" t="n">
         <v>8</v>
       </c>
-      <c r="F31" t="n">
-        <v>2025</v>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="32">
@@ -1513,18 +1513,18 @@
       <c r="E32" t="n">
         <v>7</v>
       </c>
-      <c r="F32" t="n">
-        <v>2025</v>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="33">
@@ -1547,18 +1547,18 @@
       <c r="E33" t="n">
         <v>7</v>
       </c>
-      <c r="F33" t="n">
-        <v>2025</v>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H33" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="34">
@@ -1581,18 +1581,18 @@
       <c r="E34" t="n">
         <v>8</v>
       </c>
-      <c r="F34" t="n">
-        <v>2025</v>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H34" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="35">
@@ -1615,18 +1615,18 @@
       <c r="E35" t="n">
         <v>7</v>
       </c>
-      <c r="F35" t="n">
-        <v>2025</v>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="36">
@@ -1649,18 +1649,18 @@
       <c r="E36" t="n">
         <v>7</v>
       </c>
-      <c r="F36" t="n">
-        <v>2025</v>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H36" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="37">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>agus</t>
+          <t>Agus</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1683,18 +1683,18 @@
       <c r="E37" t="n">
         <v>6</v>
       </c>
-      <c r="F37" t="n">
-        <v>2025</v>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H37" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="38">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>winda</t>
+          <t>Winda</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1717,18 +1717,18 @@
       <c r="E38" t="n">
         <v>6</v>
       </c>
-      <c r="F38" t="n">
-        <v>2025</v>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
           <t>Cumlaude (Dengan Pujian)</t>
         </is>
+      </c>
+      <c r="H38" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="39">
@@ -1751,18 +1751,18 @@
       <c r="E39" t="n">
         <v>6</v>
       </c>
-      <c r="F39" t="n">
-        <v>2025</v>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H39" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="40">
@@ -1785,18 +1785,18 @@
       <c r="E40" t="n">
         <v>8</v>
       </c>
-      <c r="F40" t="n">
-        <v>2025</v>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
           <t>Cumlaude (Dengan Pujian)</t>
         </is>
+      </c>
+      <c r="H40" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="41">
@@ -1819,18 +1819,18 @@
       <c r="E41" t="n">
         <v>8</v>
       </c>
-      <c r="F41" t="n">
-        <v>2025</v>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
           <t>Cumlaude (Dengan Pujian)</t>
         </is>
+      </c>
+      <c r="H41" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="42">
@@ -1853,18 +1853,18 @@
       <c r="E42" t="n">
         <v>8</v>
       </c>
-      <c r="F42" t="n">
-        <v>2025</v>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="43">
@@ -1887,18 +1887,18 @@
       <c r="E43" t="n">
         <v>6</v>
       </c>
-      <c r="F43" t="n">
-        <v>2025</v>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H43" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="44">
@@ -1921,18 +1921,18 @@
       <c r="E44" t="n">
         <v>6</v>
       </c>
-      <c r="F44" t="n">
-        <v>2025</v>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H44" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="45">
@@ -1955,18 +1955,18 @@
       <c r="E45" t="n">
         <v>8</v>
       </c>
-      <c r="F45" t="n">
-        <v>2025</v>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
           <t>Cumlaude (Dengan Pujian)</t>
         </is>
+      </c>
+      <c r="H45" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="46">
@@ -1989,18 +1989,18 @@
       <c r="E46" t="n">
         <v>8</v>
       </c>
-      <c r="F46" t="n">
-        <v>2025</v>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H46" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="47">
@@ -2023,18 +2023,18 @@
       <c r="E47" t="n">
         <v>8</v>
       </c>
-      <c r="F47" t="n">
-        <v>2025</v>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H47" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="48">
@@ -2057,18 +2057,18 @@
       <c r="E48" t="n">
         <v>8</v>
       </c>
-      <c r="F48" t="n">
-        <v>2025</v>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H48" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="49">
@@ -2091,18 +2091,18 @@
       <c r="E49" t="n">
         <v>8</v>
       </c>
-      <c r="F49" t="n">
-        <v>2025</v>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="50">
@@ -2125,18 +2125,18 @@
       <c r="E50" t="n">
         <v>6</v>
       </c>
-      <c r="F50" t="n">
-        <v>2025</v>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
           <t>Cumlaude (Dengan Pujian)</t>
         </is>
+      </c>
+      <c r="H50" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="51">
@@ -2159,18 +2159,18 @@
       <c r="E51" t="n">
         <v>6</v>
       </c>
-      <c r="F51" t="n">
-        <v>2025</v>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H51" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="52">
@@ -2193,18 +2193,18 @@
       <c r="E52" t="n">
         <v>8</v>
       </c>
-      <c r="F52" t="n">
-        <v>2025</v>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="53">
@@ -2227,18 +2227,18 @@
       <c r="E53" t="n">
         <v>6</v>
       </c>
-      <c r="F53" t="n">
-        <v>2025</v>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="54">
@@ -2261,18 +2261,18 @@
       <c r="E54" t="n">
         <v>6</v>
       </c>
-      <c r="F54" t="n">
-        <v>2025</v>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
           <t>Cumlaude (Dengan Pujian)</t>
         </is>
+      </c>
+      <c r="H54" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="55">
@@ -2295,18 +2295,18 @@
       <c r="E55" t="n">
         <v>6</v>
       </c>
-      <c r="F55" t="n">
-        <v>2025</v>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H55" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="56">
@@ -2329,18 +2329,18 @@
       <c r="E56" t="n">
         <v>6</v>
       </c>
-      <c r="F56" t="n">
-        <v>2025</v>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H56" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="57">
@@ -2363,18 +2363,18 @@
       <c r="E57" t="n">
         <v>7</v>
       </c>
-      <c r="F57" t="n">
-        <v>2025</v>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
           <t>Cumlaude (Dengan Pujian)</t>
         </is>
+      </c>
+      <c r="H57" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="58">
@@ -2397,18 +2397,18 @@
       <c r="E58" t="n">
         <v>7</v>
       </c>
-      <c r="F58" t="n">
-        <v>2025</v>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H58" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="59">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>sinta permata</t>
+          <t>Sinta Permata</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2431,18 +2431,18 @@
       <c r="E59" t="n">
         <v>8</v>
       </c>
-      <c r="F59" t="n">
-        <v>2025</v>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
           <t>Cumlaude (Dengan Pujian)</t>
         </is>
+      </c>
+      <c r="H59" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="60">
@@ -2465,18 +2465,18 @@
       <c r="E60" t="n">
         <v>8</v>
       </c>
-      <c r="F60" t="n">
-        <v>2025</v>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="61">
@@ -2499,18 +2499,18 @@
       <c r="E61" t="n">
         <v>7</v>
       </c>
-      <c r="F61" t="n">
-        <v>2025</v>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
           <t>Cumlaude (Dengan Pujian)</t>
         </is>
+      </c>
+      <c r="H61" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="62">
@@ -2533,18 +2533,18 @@
       <c r="E62" t="n">
         <v>6</v>
       </c>
-      <c r="F62" t="n">
-        <v>2025</v>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="63">
@@ -2567,18 +2567,18 @@
       <c r="E63" t="n">
         <v>8</v>
       </c>
-      <c r="F63" t="n">
-        <v>2025</v>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="64">
@@ -2601,18 +2601,18 @@
       <c r="E64" t="n">
         <v>7</v>
       </c>
-      <c r="F64" t="n">
-        <v>2025</v>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="65">
@@ -2635,18 +2635,18 @@
       <c r="E65" t="n">
         <v>8</v>
       </c>
-      <c r="F65" t="n">
-        <v>2025</v>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H65" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="66">
@@ -2669,18 +2669,18 @@
       <c r="E66" t="n">
         <v>8</v>
       </c>
-      <c r="F66" t="n">
-        <v>2025</v>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H66" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="67">
@@ -2703,18 +2703,18 @@
       <c r="E67" t="n">
         <v>8</v>
       </c>
-      <c r="F67" t="n">
-        <v>2025</v>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H67" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="68">
@@ -2737,18 +2737,18 @@
       <c r="E68" t="n">
         <v>8</v>
       </c>
-      <c r="F68" t="n">
-        <v>2025</v>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H68" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="69">
@@ -2771,18 +2771,18 @@
       <c r="E69" t="n">
         <v>6</v>
       </c>
-      <c r="F69" t="n">
-        <v>2025</v>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="70">
@@ -2805,18 +2805,18 @@
       <c r="E70" t="n">
         <v>8</v>
       </c>
-      <c r="F70" t="n">
-        <v>2025</v>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H70" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="71">
@@ -2839,18 +2839,18 @@
       <c r="E71" t="n">
         <v>8</v>
       </c>
-      <c r="F71" t="n">
-        <v>2025</v>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H71" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="72">
@@ -2873,18 +2873,18 @@
       <c r="E72" t="n">
         <v>9</v>
       </c>
-      <c r="F72" t="n">
-        <v>2025</v>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="73">
@@ -2907,18 +2907,18 @@
       <c r="E73" t="n">
         <v>9</v>
       </c>
-      <c r="F73" t="n">
-        <v>2025</v>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H73" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="74">
@@ -2941,18 +2941,18 @@
       <c r="E74" t="n">
         <v>10</v>
       </c>
-      <c r="F74" t="n">
-        <v>2025</v>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H74" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="75">
@@ -2975,18 +2975,18 @@
       <c r="E75" t="n">
         <v>10</v>
       </c>
-      <c r="F75" t="n">
-        <v>2025</v>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="76">
@@ -3009,18 +3009,18 @@
       <c r="E76" t="n">
         <v>10</v>
       </c>
-      <c r="F76" t="n">
-        <v>2025</v>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="77">
@@ -3043,18 +3043,18 @@
       <c r="E77" t="n">
         <v>9</v>
       </c>
-      <c r="F77" t="n">
-        <v>2025</v>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H77" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="78">
@@ -3077,18 +3077,18 @@
       <c r="E78" t="n">
         <v>10</v>
       </c>
-      <c r="F78" t="n">
-        <v>2025</v>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="79">
@@ -3111,18 +3111,18 @@
       <c r="E79" t="n">
         <v>10</v>
       </c>
-      <c r="F79" t="n">
-        <v>2025</v>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="80">
@@ -3145,18 +3145,18 @@
       <c r="E80" t="n">
         <v>9</v>
       </c>
-      <c r="F80" t="n">
-        <v>2025</v>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="81">
@@ -3179,18 +3179,18 @@
       <c r="E81" t="n">
         <v>8</v>
       </c>
-      <c r="F81" t="n">
-        <v>2025</v>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H81" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="82">
@@ -3213,18 +3213,18 @@
       <c r="E82" t="n">
         <v>10</v>
       </c>
-      <c r="F82" t="n">
-        <v>2025</v>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H82" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="83">
@@ -3247,18 +3247,18 @@
       <c r="E83" t="n">
         <v>9</v>
       </c>
-      <c r="F83" t="n">
-        <v>2025</v>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H83" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="84">
@@ -3281,18 +3281,18 @@
       <c r="E84" t="n">
         <v>10</v>
       </c>
-      <c r="F84" t="n">
-        <v>2025</v>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="85">
@@ -3315,18 +3315,18 @@
       <c r="E85" t="n">
         <v>10</v>
       </c>
-      <c r="F85" t="n">
-        <v>2025</v>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="86">
@@ -3349,18 +3349,18 @@
       <c r="E86" t="n">
         <v>9</v>
       </c>
-      <c r="F86" t="n">
-        <v>2025</v>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H86" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="87">
@@ -3383,18 +3383,18 @@
       <c r="E87" t="n">
         <v>9</v>
       </c>
-      <c r="F87" t="n">
-        <v>2025</v>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H87" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="88">
@@ -3417,18 +3417,18 @@
       <c r="E88" t="n">
         <v>9</v>
       </c>
-      <c r="F88" t="n">
-        <v>2025</v>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H88" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="89">
@@ -3451,18 +3451,18 @@
       <c r="E89" t="n">
         <v>8</v>
       </c>
-      <c r="F89" t="n">
-        <v>2025</v>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="90">
@@ -3485,18 +3485,18 @@
       <c r="E90" t="n">
         <v>10</v>
       </c>
-      <c r="F90" t="n">
-        <v>2025</v>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="91">
@@ -3519,18 +3519,18 @@
       <c r="E91" t="n">
         <v>8</v>
       </c>
-      <c r="F91" t="n">
-        <v>2025</v>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H91" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="92">
@@ -3553,18 +3553,18 @@
       <c r="E92" t="n">
         <v>10</v>
       </c>
-      <c r="F92" t="n">
-        <v>2025</v>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="93">
@@ -3587,18 +3587,18 @@
       <c r="E93" t="n">
         <v>10</v>
       </c>
-      <c r="F93" t="n">
-        <v>2025</v>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H93" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="94">
@@ -3621,18 +3621,18 @@
       <c r="E94" t="n">
         <v>10</v>
       </c>
-      <c r="F94" t="n">
-        <v>2025</v>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="95">
@@ -3655,18 +3655,18 @@
       <c r="E95" t="n">
         <v>10</v>
       </c>
-      <c r="F95" t="n">
-        <v>2025</v>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="96">
@@ -3689,18 +3689,18 @@
       <c r="E96" t="n">
         <v>9</v>
       </c>
-      <c r="F96" t="n">
-        <v>2025</v>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H96" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="97">
@@ -3723,18 +3723,18 @@
       <c r="E97" t="n">
         <v>10</v>
       </c>
-      <c r="F97" t="n">
-        <v>2025</v>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H97" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="98">
@@ -3757,18 +3757,18 @@
       <c r="E98" t="n">
         <v>10</v>
       </c>
-      <c r="F98" t="n">
-        <v>2025</v>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="99">
@@ -3791,18 +3791,18 @@
       <c r="E99" t="n">
         <v>10</v>
       </c>
-      <c r="F99" t="n">
-        <v>2025</v>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="100">
@@ -3825,18 +3825,18 @@
       <c r="E100" t="n">
         <v>10</v>
       </c>
-      <c r="F100" t="n">
-        <v>2025</v>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="101">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>budi wijaya</t>
+          <t>Budi Wijaya</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3859,18 +3859,18 @@
       <c r="E101" t="n">
         <v>9</v>
       </c>
-      <c r="F101" t="n">
-        <v>2025</v>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="102">
@@ -3893,18 +3893,18 @@
       <c r="E102" t="n">
         <v>9</v>
       </c>
-      <c r="F102" t="n">
-        <v>2025</v>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H102" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="103">
@@ -3927,18 +3927,18 @@
       <c r="E103" t="n">
         <v>9</v>
       </c>
-      <c r="F103" t="n">
-        <v>2025</v>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H103" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="104">
@@ -3961,18 +3961,18 @@
       <c r="E104" t="n">
         <v>10</v>
       </c>
-      <c r="F104" t="n">
-        <v>2025</v>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H104" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="105">
@@ -3995,18 +3995,18 @@
       <c r="E105" t="n">
         <v>9</v>
       </c>
-      <c r="F105" t="n">
-        <v>2025</v>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H105" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="106">
@@ -4029,18 +4029,18 @@
       <c r="E106" t="n">
         <v>8</v>
       </c>
-      <c r="F106" t="n">
-        <v>2025</v>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H106" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="107">
@@ -4063,18 +4063,18 @@
       <c r="E107" t="n">
         <v>9</v>
       </c>
-      <c r="F107" t="n">
-        <v>2025</v>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H107" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="108">
@@ -4097,18 +4097,18 @@
       <c r="E108" t="n">
         <v>9</v>
       </c>
-      <c r="F108" t="n">
-        <v>2025</v>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="109">
@@ -4131,18 +4131,18 @@
       <c r="E109" t="n">
         <v>8</v>
       </c>
-      <c r="F109" t="n">
-        <v>2025</v>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H109" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="110">
@@ -4165,18 +4165,18 @@
       <c r="E110" t="n">
         <v>8</v>
       </c>
-      <c r="F110" t="n">
-        <v>2025</v>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H110" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="111">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PUTRI</t>
+          <t>Putri</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4199,18 +4199,18 @@
       <c r="E111" t="n">
         <v>9</v>
       </c>
-      <c r="F111" t="n">
-        <v>2025</v>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H111" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="112">
@@ -4233,18 +4233,18 @@
       <c r="E112" t="n">
         <v>8</v>
       </c>
-      <c r="F112" t="n">
-        <v>2025</v>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H112" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="113">
@@ -4267,18 +4267,18 @@
       <c r="E113" t="n">
         <v>9</v>
       </c>
-      <c r="F113" t="n">
-        <v>2025</v>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H113" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="114">
@@ -4301,18 +4301,18 @@
       <c r="E114" t="n">
         <v>8</v>
       </c>
-      <c r="F114" t="n">
-        <v>2025</v>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H114" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="115">
@@ -4335,18 +4335,18 @@
       <c r="E115" t="n">
         <v>9</v>
       </c>
-      <c r="F115" t="n">
-        <v>2025</v>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="116">
@@ -4369,18 +4369,18 @@
       <c r="E116" t="n">
         <v>10</v>
       </c>
-      <c r="F116" t="n">
-        <v>2025</v>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H116" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="117">
@@ -4403,18 +4403,18 @@
       <c r="E117" t="n">
         <v>8</v>
       </c>
-      <c r="F117" t="n">
-        <v>2025</v>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H117" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="118">
@@ -4437,18 +4437,18 @@
       <c r="E118" t="n">
         <v>10</v>
       </c>
-      <c r="F118" t="n">
-        <v>2025</v>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="119">
@@ -4471,18 +4471,18 @@
       <c r="E119" t="n">
         <v>8</v>
       </c>
-      <c r="F119" t="n">
-        <v>2025</v>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="120">
@@ -4505,18 +4505,18 @@
       <c r="E120" t="n">
         <v>10</v>
       </c>
-      <c r="F120" t="n">
-        <v>2025</v>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H120" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="121">
@@ -4539,18 +4539,18 @@
       <c r="E121" t="n">
         <v>10</v>
       </c>
-      <c r="F121" t="n">
-        <v>2025</v>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="122">
@@ -4573,18 +4573,18 @@
       <c r="E122" t="n">
         <v>10</v>
       </c>
-      <c r="F122" t="n">
-        <v>2025</v>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="123">
@@ -4607,18 +4607,18 @@
       <c r="E123" t="n">
         <v>8</v>
       </c>
-      <c r="F123" t="n">
-        <v>2025</v>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H123" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="124">
@@ -4641,18 +4641,18 @@
       <c r="E124" t="n">
         <v>9</v>
       </c>
-      <c r="F124" t="n">
-        <v>2025</v>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="125">
@@ -4675,18 +4675,18 @@
       <c r="E125" t="n">
         <v>8</v>
       </c>
-      <c r="F125" t="n">
-        <v>2025</v>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H125" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="126">
@@ -4709,18 +4709,18 @@
       <c r="E126" t="n">
         <v>8</v>
       </c>
-      <c r="F126" t="n">
-        <v>2025</v>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="127">
@@ -4743,18 +4743,18 @@
       <c r="E127" t="n">
         <v>9</v>
       </c>
-      <c r="F127" t="n">
-        <v>2025</v>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H127" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="128">
@@ -4777,18 +4777,18 @@
       <c r="E128" t="n">
         <v>10</v>
       </c>
-      <c r="F128" t="n">
-        <v>2025</v>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="129">
@@ -4811,18 +4811,18 @@
       <c r="E129" t="n">
         <v>8</v>
       </c>
-      <c r="F129" t="n">
-        <v>2025</v>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H129" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="130">
@@ -4845,18 +4845,18 @@
       <c r="E130" t="n">
         <v>9</v>
       </c>
-      <c r="F130" t="n">
-        <v>2025</v>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="131">
@@ -4879,18 +4879,18 @@
       <c r="E131" t="n">
         <v>9</v>
       </c>
-      <c r="F131" t="n">
-        <v>2025</v>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H131" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="132">
@@ -4913,18 +4913,18 @@
       <c r="E132" t="n">
         <v>9</v>
       </c>
-      <c r="F132" t="n">
-        <v>2025</v>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H132" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="133">
@@ -4947,18 +4947,18 @@
       <c r="E133" t="n">
         <v>9</v>
       </c>
-      <c r="F133" t="n">
-        <v>2025</v>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H133" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="134">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>BUDI MAULANA</t>
+          <t>Budi Maulana</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4981,18 +4981,18 @@
       <c r="E134" t="n">
         <v>8</v>
       </c>
-      <c r="F134" t="n">
-        <v>2025</v>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="135">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>AULIA PERMATA</t>
+          <t>Aulia Permata</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5015,18 +5015,18 @@
       <c r="E135" t="n">
         <v>9</v>
       </c>
-      <c r="F135" t="n">
-        <v>2025</v>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H135" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="136">
@@ -5049,18 +5049,18 @@
       <c r="E136" t="n">
         <v>9</v>
       </c>
-      <c r="F136" t="n">
-        <v>2025</v>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="137">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>rina sari kurniawan</t>
+          <t>Rina Sari Kurniawan</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5083,18 +5083,18 @@
       <c r="E137" t="n">
         <v>9</v>
       </c>
-      <c r="F137" t="n">
-        <v>2025</v>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H137" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="138">
@@ -5117,18 +5117,18 @@
       <c r="E138" t="n">
         <v>9</v>
       </c>
-      <c r="F138" t="n">
-        <v>2025</v>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H138" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="139">
@@ -5151,18 +5151,18 @@
       <c r="E139" t="n">
         <v>10</v>
       </c>
-      <c r="F139" t="n">
-        <v>2025</v>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="140">
@@ -5185,18 +5185,18 @@
       <c r="E140" t="n">
         <v>9</v>
       </c>
-      <c r="F140" t="n">
-        <v>2025</v>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H140" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="141">
@@ -5219,18 +5219,18 @@
       <c r="E141" t="n">
         <v>9</v>
       </c>
-      <c r="F141" t="n">
-        <v>2025</v>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H141" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="142">
@@ -5253,18 +5253,18 @@
       <c r="E142" t="n">
         <v>9</v>
       </c>
-      <c r="F142" t="n">
-        <v>2025</v>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H142" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="143">
@@ -5287,18 +5287,18 @@
       <c r="E143" t="n">
         <v>9</v>
       </c>
-      <c r="F143" t="n">
-        <v>2025</v>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H143" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="144">
@@ -5321,18 +5321,18 @@
       <c r="E144" t="n">
         <v>8</v>
       </c>
-      <c r="F144" t="n">
-        <v>2025</v>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="145">
@@ -5355,18 +5355,18 @@
       <c r="E145" t="n">
         <v>9</v>
       </c>
-      <c r="F145" t="n">
-        <v>2025</v>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H145" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="146">
@@ -5389,18 +5389,18 @@
       <c r="E146" t="n">
         <v>9</v>
       </c>
-      <c r="F146" t="n">
-        <v>2025</v>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H146" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="147">
@@ -5423,18 +5423,18 @@
       <c r="E147" t="n">
         <v>9</v>
       </c>
-      <c r="F147" t="n">
-        <v>2025</v>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H147" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="148">
@@ -5457,18 +5457,18 @@
       <c r="E148" t="n">
         <v>9</v>
       </c>
-      <c r="F148" t="n">
-        <v>2025</v>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="149">
@@ -5491,18 +5491,18 @@
       <c r="E149" t="n">
         <v>8</v>
       </c>
-      <c r="F149" t="n">
-        <v>2025</v>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="150">
@@ -5525,18 +5525,18 @@
       <c r="E150" t="n">
         <v>10</v>
       </c>
-      <c r="F150" t="n">
-        <v>2025</v>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H150" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="151">
@@ -5559,18 +5559,18 @@
       <c r="E151" t="n">
         <v>9</v>
       </c>
-      <c r="F151" t="n">
-        <v>2025</v>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H151" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="152">
@@ -5593,18 +5593,18 @@
       <c r="E152" t="n">
         <v>9</v>
       </c>
-      <c r="F152" t="n">
-        <v>2025</v>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H152" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="153">
@@ -5627,18 +5627,18 @@
       <c r="E153" t="n">
         <v>10</v>
       </c>
-      <c r="F153" t="n">
-        <v>2025</v>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H153" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="154">
@@ -5661,18 +5661,18 @@
       <c r="E154" t="n">
         <v>10</v>
       </c>
-      <c r="F154" t="n">
-        <v>2025</v>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H154" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="155">
@@ -5695,18 +5695,18 @@
       <c r="E155" t="n">
         <v>9</v>
       </c>
-      <c r="F155" t="n">
-        <v>2025</v>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H155" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="156">
@@ -5729,18 +5729,18 @@
       <c r="E156" t="n">
         <v>10</v>
       </c>
-      <c r="F156" t="n">
-        <v>2025</v>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H156" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="157">
@@ -5763,18 +5763,18 @@
       <c r="E157" t="n">
         <v>8</v>
       </c>
-      <c r="F157" t="n">
-        <v>2025</v>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="158">
@@ -5797,18 +5797,18 @@
       <c r="E158" t="n">
         <v>8</v>
       </c>
-      <c r="F158" t="n">
-        <v>2025</v>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
           <t>Cumlaude (Dengan Pujian)</t>
         </is>
+      </c>
+      <c r="H158" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="159">
@@ -5831,18 +5831,18 @@
       <c r="E159" t="n">
         <v>9</v>
       </c>
-      <c r="F159" t="n">
-        <v>2025</v>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H159" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="160">
@@ -5865,18 +5865,18 @@
       <c r="E160" t="n">
         <v>8</v>
       </c>
-      <c r="F160" t="n">
-        <v>2025</v>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H160" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="161">
@@ -5899,18 +5899,18 @@
       <c r="E161" t="n">
         <v>8</v>
       </c>
-      <c r="F161" t="n">
-        <v>2025</v>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H161" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="162">
@@ -5933,18 +5933,18 @@
       <c r="E162" t="n">
         <v>10</v>
       </c>
-      <c r="F162" t="n">
-        <v>2025</v>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H162" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="163">
@@ -5967,18 +5967,18 @@
       <c r="E163" t="n">
         <v>10</v>
       </c>
-      <c r="F163" t="n">
-        <v>2025</v>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H163" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="164">
@@ -6001,18 +6001,18 @@
       <c r="E164" t="n">
         <v>10</v>
       </c>
-      <c r="F164" t="n">
-        <v>2025</v>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H164" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="165">
@@ -6035,18 +6035,18 @@
       <c r="E165" t="n">
         <v>8</v>
       </c>
-      <c r="F165" t="n">
-        <v>2025</v>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H165" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="166">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>nina</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6069,18 +6069,18 @@
       <c r="E166" t="n">
         <v>9</v>
       </c>
-      <c r="F166" t="n">
-        <v>2025</v>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H166" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="167">
@@ -6103,18 +6103,18 @@
       <c r="E167" t="n">
         <v>9</v>
       </c>
-      <c r="F167" t="n">
-        <v>2025</v>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H167" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="168">
@@ -6137,18 +6137,18 @@
       <c r="E168" t="n">
         <v>9</v>
       </c>
-      <c r="F168" t="n">
-        <v>2025</v>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H168" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="169">
@@ -6171,18 +6171,18 @@
       <c r="E169" t="n">
         <v>9</v>
       </c>
-      <c r="F169" t="n">
-        <v>2025</v>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H169" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="170">
@@ -6205,18 +6205,18 @@
       <c r="E170" t="n">
         <v>10</v>
       </c>
-      <c r="F170" t="n">
-        <v>2025</v>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H170" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="171">
@@ -6239,18 +6239,18 @@
       <c r="E171" t="n">
         <v>10</v>
       </c>
-      <c r="F171" t="n">
-        <v>2025</v>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H171" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="172">
@@ -6273,18 +6273,18 @@
       <c r="E172" t="n">
         <v>8</v>
       </c>
-      <c r="F172" t="n">
-        <v>2025</v>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H172" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="173">
@@ -6307,18 +6307,18 @@
       <c r="E173" t="n">
         <v>8</v>
       </c>
-      <c r="F173" t="n">
-        <v>2025</v>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H173" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="174">
@@ -6341,18 +6341,18 @@
       <c r="E174" t="n">
         <v>9</v>
       </c>
-      <c r="F174" t="n">
-        <v>2025</v>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H174" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="175">
@@ -6375,18 +6375,18 @@
       <c r="E175" t="n">
         <v>10</v>
       </c>
-      <c r="F175" t="n">
-        <v>2025</v>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H175" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="176">
@@ -6409,18 +6409,18 @@
       <c r="E176" t="n">
         <v>8</v>
       </c>
-      <c r="F176" t="n">
-        <v>2025</v>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H176" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="177">
@@ -6443,18 +6443,18 @@
       <c r="E177" t="n">
         <v>9</v>
       </c>
-      <c r="F177" t="n">
-        <v>2025</v>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H177" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="178">
@@ -6477,18 +6477,18 @@
       <c r="E178" t="n">
         <v>8</v>
       </c>
-      <c r="F178" t="n">
-        <v>2025</v>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H178" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="179">
@@ -6511,18 +6511,18 @@
       <c r="E179" t="n">
         <v>8</v>
       </c>
-      <c r="F179" t="n">
-        <v>2025</v>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H179" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="180">
@@ -6545,18 +6545,18 @@
       <c r="E180" t="n">
         <v>9</v>
       </c>
-      <c r="F180" t="n">
-        <v>2025</v>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H180" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="181">
@@ -6579,18 +6579,18 @@
       <c r="E181" t="n">
         <v>8</v>
       </c>
-      <c r="F181" t="n">
-        <v>2025</v>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
           <t>Cumlaude (Dengan Pujian)</t>
         </is>
+      </c>
+      <c r="H181" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="182">
@@ -6613,18 +6613,18 @@
       <c r="E182" t="n">
         <v>9</v>
       </c>
-      <c r="F182" t="n">
-        <v>2025</v>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H182" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="183">
@@ -6647,18 +6647,18 @@
       <c r="E183" t="n">
         <v>8</v>
       </c>
-      <c r="F183" t="n">
-        <v>2025</v>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
           <t>Cumlaude (Dengan Pujian)</t>
         </is>
+      </c>
+      <c r="H183" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="184">
@@ -6681,18 +6681,18 @@
       <c r="E184" t="n">
         <v>10</v>
       </c>
-      <c r="F184" t="n">
-        <v>2025</v>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H184" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="185">
@@ -6715,18 +6715,18 @@
       <c r="E185" t="n">
         <v>10</v>
       </c>
-      <c r="F185" t="n">
-        <v>2025</v>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>B+</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H185" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="186">
@@ -6749,18 +6749,18 @@
       <c r="E186" t="n">
         <v>9</v>
       </c>
-      <c r="F186" t="n">
-        <v>2025</v>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H186" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="187">
@@ -6783,18 +6783,18 @@
       <c r="E187" t="n">
         <v>10</v>
       </c>
-      <c r="F187" t="n">
-        <v>2025</v>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H187" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="188">
@@ -6817,18 +6817,18 @@
       <c r="E188" t="n">
         <v>10</v>
       </c>
-      <c r="F188" t="n">
-        <v>2025</v>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H188" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="189">
@@ -6851,18 +6851,18 @@
       <c r="E189" t="n">
         <v>10</v>
       </c>
-      <c r="F189" t="n">
-        <v>2025</v>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H189" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="190">
@@ -6885,18 +6885,18 @@
       <c r="E190" t="n">
         <v>9</v>
       </c>
-      <c r="F190" t="n">
-        <v>2025</v>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H190" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="191">
@@ -6919,18 +6919,18 @@
       <c r="E191" t="n">
         <v>8</v>
       </c>
-      <c r="F191" t="n">
-        <v>2025</v>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H191" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="192">
@@ -6953,18 +6953,18 @@
       <c r="E192" t="n">
         <v>9</v>
       </c>
-      <c r="F192" t="n">
-        <v>2025</v>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H192" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="193">
@@ -6987,18 +6987,18 @@
       <c r="E193" t="n">
         <v>9</v>
       </c>
-      <c r="F193" t="n">
-        <v>2025</v>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H193" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="194">
@@ -7021,18 +7021,18 @@
       <c r="E194" t="n">
         <v>8</v>
       </c>
-      <c r="F194" t="n">
-        <v>2025</v>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H194" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="195">
@@ -7055,18 +7055,18 @@
       <c r="E195" t="n">
         <v>8</v>
       </c>
-      <c r="F195" t="n">
-        <v>2025</v>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H195" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="196">
@@ -7089,18 +7089,18 @@
       <c r="E196" t="n">
         <v>8</v>
       </c>
-      <c r="F196" t="n">
-        <v>2025</v>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H196" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="197">
@@ -7123,18 +7123,18 @@
       <c r="E197" t="n">
         <v>9</v>
       </c>
-      <c r="F197" t="n">
-        <v>2025</v>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H197" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="198">
@@ -7157,18 +7157,18 @@
       <c r="E198" t="n">
         <v>8</v>
       </c>
-      <c r="F198" t="n">
-        <v>2025</v>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H198" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="199">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>mega nugroho</t>
+          <t>Mega Nugroho</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7191,18 +7191,18 @@
       <c r="E199" t="n">
         <v>10</v>
       </c>
-      <c r="F199" t="n">
-        <v>2025</v>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H199" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="200">
@@ -7225,18 +7225,18 @@
       <c r="E200" t="n">
         <v>8</v>
       </c>
-      <c r="F200" t="n">
-        <v>2025</v>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H200" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="201">
@@ -7259,18 +7259,18 @@
       <c r="E201" t="n">
         <v>10</v>
       </c>
-      <c r="F201" t="n">
-        <v>2025</v>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H201" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="202">
@@ -7293,18 +7293,18 @@
       <c r="E202" t="n">
         <v>9</v>
       </c>
-      <c r="F202" t="n">
-        <v>2025</v>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H202" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="203">
@@ -7327,18 +7327,18 @@
       <c r="E203" t="n">
         <v>9</v>
       </c>
-      <c r="F203" t="n">
-        <v>2025</v>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H203" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="204">
@@ -7361,18 +7361,18 @@
       <c r="E204" t="n">
         <v>8</v>
       </c>
-      <c r="F204" t="n">
-        <v>2025</v>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H204" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="205">
@@ -7395,18 +7395,18 @@
       <c r="E205" t="n">
         <v>8</v>
       </c>
-      <c r="F205" t="n">
-        <v>2025</v>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H205" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="206">
@@ -7429,18 +7429,18 @@
       <c r="E206" t="n">
         <v>10</v>
       </c>
-      <c r="F206" t="n">
-        <v>2025</v>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H206" t="inlineStr">
-        <is>
           <t>Cukup</t>
         </is>
+      </c>
+      <c r="H206" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="207">
@@ -7463,18 +7463,18 @@
       <c r="E207" t="n">
         <v>9</v>
       </c>
-      <c r="F207" t="n">
-        <v>2025</v>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H207" t="n">
+        <v>2025</v>
       </c>
     </row>
   </sheetData>
@@ -7831,17 +7831,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Predikat Wisuda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Tahun Wisuda</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Grade</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Predikat Wisuda</t>
         </is>
       </c>
     </row>
@@ -7865,18 +7865,18 @@
       <c r="E2" t="n">
         <v>8</v>
       </c>
-      <c r="F2" t="n">
-        <v>2025</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
           <t>Cumlaude (Dengan Pujian)</t>
         </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="3">
@@ -7899,18 +7899,18 @@
       <c r="E3" t="n">
         <v>10</v>
       </c>
-      <c r="F3" t="n">
-        <v>2025</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="4">
@@ -7933,18 +7933,18 @@
       <c r="E4" t="n">
         <v>10</v>
       </c>
-      <c r="F4" t="n">
-        <v>2025</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Memuaskan</t>
-        </is>
+          <t>Memuaskan</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="5">
@@ -7967,18 +7967,18 @@
       <c r="E5" t="n">
         <v>9</v>
       </c>
-      <c r="F5" t="n">
-        <v>2025</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
           <t>Sangat Memuaskan</t>
         </is>
+      </c>
+      <c r="H5" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="6">
@@ -8001,18 +8001,18 @@
       <c r="E6" t="n">
         <v>7</v>
       </c>
-      <c r="F6" t="n">
-        <v>2025</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
           <t>Cumlaude (Dengan Pujian)</t>
         </is>
+      </c>
+      <c r="H6" t="n">
+        <v>2025</v>
       </c>
     </row>
   </sheetData>
